--- a/gte/nodes/LPC/compressor_stage_2_blade_stator_coordinates_lattice.xlsx
+++ b/gte/nodes/LPC/compressor_stage_2_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>13.097614535648118</v>
+        <v>12.901675497178003</v>
       </c>
       <c r="B1">
-        <v>15.647484553337955</v>
+        <v>15.809429108506343</v>
       </c>
       <c r="C1">
         <v>374.58109848544609</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>11.808662714367312</v>
+        <v>11.672554516985237</v>
       </c>
       <c r="B2">
-        <v>15.39863927168483</v>
+        <v>15.484083689206054</v>
       </c>
       <c r="C2">
         <v>374.58109848544609</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10.67201744373401</v>
+        <v>10.562602203430139</v>
       </c>
       <c r="B3">
-        <v>14.983066665973274</v>
+        <v>15.031506172472973</v>
       </c>
       <c r="C3">
         <v>374.58109848544609</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.5678873216775386</v>
+        <v>9.4807081015845913</v>
       </c>
       <c r="B4">
-        <v>14.531900294330246</v>
+        <v>14.548971912690364</v>
       </c>
       <c r="C4">
         <v>374.58109848544609</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>8.4894502951598358</v>
+        <v>8.4216412803452023</v>
       </c>
       <c r="B5">
-        <v>14.052608139208145</v>
+        <v>14.042065786777545</v>
       </c>
       <c r="C5">
         <v>374.58109848544609</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>7.4338348282855193</v>
+        <v>7.38317717751503</v>
       </c>
       <c r="B6">
-        <v>13.548333620858687</v>
+        <v>13.513162879747824</v>
       </c>
       <c r="C6">
         <v>374.58109848544609</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>6.3993484745214442</v>
+        <v>6.3639915770616167</v>
       </c>
       <c r="B7">
-        <v>13.020929430977557</v>
+        <v>12.963677009411009</v>
       </c>
       <c r="C7">
         <v>374.58109848544609</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>5.3849437820454966</v>
+        <v>5.3632525030845413</v>
       </c>
       <c r="B8">
-        <v>12.471542196801989</v>
+        <v>12.394496446499764</v>
       </c>
       <c r="C8">
         <v>374.58109848544609</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4.3890768947303416</v>
+        <v>4.3797547619622135</v>
       </c>
       <c r="B9">
-        <v>11.901861950702541</v>
+        <v>11.806907932878488</v>
       </c>
       <c r="C9">
         <v>374.58109848544609</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.4100981821639231</v>
+        <v>3.4122146917757377</v>
       </c>
       <c r="B10">
-        <v>11.313694514314053</v>
+        <v>11.202281988189158</v>
       </c>
       <c r="C10">
         <v>374.58109848544609</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2.4464313211005271</v>
+        <v>2.4594079751382005</v>
       </c>
       <c r="B11">
-        <v>10.708765461195187</v>
+        <v>10.581925772052301</v>
       </c>
       <c r="C11">
         <v>374.58109848544609</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.4971947957615386</v>
+        <v>1.520640204587205</v>
       </c>
       <c r="B12">
-        <v>10.088039771291053</v>
+        <v>9.946580678329294</v>
       </c>
       <c r="C12">
         <v>374.58109848544609</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.56421301307040073</v>
+        <v>0.59727726782643831</v>
       </c>
       <c r="B13">
-        <v>9.4495202981687143</v>
+        <v>9.294788397866391</v>
       </c>
       <c r="C13">
         <v>374.58109848544609</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.35144884568769597</v>
+        <v>-0.30989040918569505</v>
       </c>
       <c r="B14">
-        <v>8.7920410064569925</v>
+        <v>8.6257050213089688</v>
       </c>
       <c r="C14">
         <v>374.58109848544609</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.254468424482607</v>
+        <v>-1.2044345426380043</v>
       </c>
       <c r="B15">
-        <v>8.1207224314098</v>
+        <v>7.9431439415140508</v>
       </c>
       <c r="C15">
         <v>374.58109848544609</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.1491356806706854</v>
+        <v>-2.0896307333130695</v>
       </c>
       <c r="B16">
-        <v>7.4402607145083</v>
+        <v>7.2506023995742757</v>
       </c>
       <c r="C16">
         <v>374.58109848544609</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.03244699989923</v>
+        <v>-2.9632079782213543</v>
       </c>
       <c r="B17">
-        <v>6.7473678515176134</v>
+        <v>6.5456557273131191</v>
       </c>
       <c r="C17">
         <v>374.58109848544609</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.9005031564963972</v>
+        <v>-3.8222126942336949</v>
       </c>
       <c r="B18">
-        <v>6.0377754281154248</v>
+        <v>5.8251504902996327</v>
       </c>
       <c r="C18">
         <v>374.58109848544609</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.7531160512228423</v>
+        <v>-4.6665075814345363</v>
       </c>
       <c r="B19">
-        <v>5.3112775353457478</v>
+        <v>5.088940098354314</v>
       </c>
       <c r="C19">
         <v>374.58109848544609</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-5.5910253664473437</v>
+        <v>-5.4966594107117261</v>
       </c>
       <c r="B20">
-        <v>4.5686838905941825</v>
+        <v>4.3376296723605243</v>
       </c>
       <c r="C20">
         <v>374.58109848544609</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-6.4149707845386814</v>
+        <v>-6.3132349529531133</v>
       </c>
       <c r="B21">
-        <v>3.8108042112463245</v>
+        <v>3.5718243332016257</v>
       </c>
       <c r="C21">
         <v>374.58109848544609</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-7.2255577313199462</v>
+        <v>-7.11669745532941</v>
       </c>
       <c r="B22">
-        <v>3.0383012463892687</v>
+        <v>2.7920186732131933</v>
       </c>
       <c r="C22">
         <v>374.58109848544609</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-8.022854606431487</v>
+        <v>-7.9070960701428</v>
       </c>
       <c r="B23">
-        <v>2.2512498719160914</v>
+        <v>1.9982651705396575</v>
       </c>
       <c r="C23">
         <v>374.58109848544609</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-8.8067955529679587</v>
+        <v>-8.6843764259783214</v>
       </c>
       <c r="B24">
-        <v>1.4495779954213679</v>
+        <v>1.1905057747776726</v>
       </c>
       <c r="C24">
         <v>374.58109848544609</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-9.5773147140240162</v>
+        <v>-9.448484151421022</v>
       </c>
       <c r="B25">
-        <v>0.63321352449966994</v>
+        <v>0.3686824355238873</v>
       </c>
       <c r="C25">
         <v>374.58109848544609</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-10.3343194115617</v>
+        <v>-10.19934303767011</v>
       </c>
       <c r="B26">
-        <v>-0.19794499388042092</v>
+        <v>-0.46728621261614944</v>
       </c>
       <c r="C26">
         <v>374.58109848544609</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-11.077609683012561</v>
+        <v>-10.936789526381457</v>
       </c>
       <c r="B27">
-        <v>-1.0441164552543145</v>
+        <v>-1.3175747950013106</v>
       </c>
       <c r="C27">
         <v>374.58109848544609</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-11.806958744675532</v>
+        <v>-11.660638221825085</v>
       </c>
       <c r="B28">
-        <v>-1.9055491157834024</v>
+        <v>-2.1823812519815515</v>
       </c>
       <c r="C28">
         <v>374.58109848544609</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-12.522139812849543</v>
+        <v>-12.37070372827103</v>
       </c>
       <c r="B29">
-        <v>-2.7824912316290793</v>
+        <v>-3.061903523906842</v>
       </c>
       <c r="C29">
         <v>374.58109848544609</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-13.223015741069958</v>
+        <v>-13.06686721445393</v>
       </c>
       <c r="B30">
-        <v>-3.6750929346337102</v>
+        <v>-3.9562684826434085</v>
       </c>
       <c r="C30">
         <v>374.58109848544609</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-13.909807931817891</v>
+        <v>-13.749276106966867</v>
       </c>
       <c r="B31">
-        <v>-4.5831118593635072</v>
+        <v>-4.8653187261225321</v>
       </c>
       <c r="C31">
         <v>374.58109848544609</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-14.58282742481089</v>
+        <v>-14.418144396867536</v>
       </c>
       <c r="B32">
-        <v>-5.5062075160656585</v>
+        <v>-5.7888257837917587</v>
       </c>
       <c r="C32">
         <v>374.58109848544609</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-15.242385259766502</v>
+        <v>-15.07368607521363</v>
       </c>
       <c r="B33">
-        <v>-6.4440394149873432</v>
+        <v>-6.7265611850986327</v>
       </c>
       <c r="C33">
         <v>374.58109848544609</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-15.888630383398404</v>
+        <v>-15.715990034285172</v>
       </c>
       <c r="B34">
-        <v>-7.3964445067594236</v>
+        <v>-7.6784300229542968</v>
       </c>
       <c r="C34">
         <v>374.58109848544609</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-16.521063370404779</v>
+        <v>-16.344644771251538</v>
       </c>
       <c r="B35">
-        <v>-8.363969503547489</v>
+        <v>-8.6448716441242848</v>
       </c>
       <c r="C35">
         <v>374.58109848544609</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-17.139022702479952</v>
+        <v>-16.959113684504427</v>
       </c>
       <c r="B36">
-        <v>-9.3473385579008141</v>
+        <v>-9.6264589588377358</v>
       </c>
       <c r="C36">
         <v>374.58109848544609</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-17.741846861318233</v>
+        <v>-17.558860172435548</v>
       </c>
       <c r="B37">
-        <v>-10.347275822368671</v>
+        <v>-10.623764877323787</v>
       </c>
       <c r="C37">
         <v>374.58109848544609</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-18.328487059824717</v>
+        <v>-18.143051261887177</v>
       </c>
       <c r="B38">
-        <v>-11.36492938588813</v>
+        <v>-11.637678735050834</v>
       </c>
       <c r="C38">
         <v>374.58109848544609</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-18.896345435747541</v>
+        <v>-18.709668493503866</v>
       </c>
       <c r="B39">
-        <v>-12.403143082947473</v>
+        <v>-12.670355568444322</v>
       </c>
       <c r="C39">
         <v>374.58109848544609</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-19.442436858045646</v>
+        <v>-19.256397036380744</v>
       </c>
       <c r="B40">
-        <v>-13.465184684422795</v>
+        <v>-13.724266839168969</v>
       </c>
       <c r="C40">
         <v>374.58109848544609</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-19.963776195677941</v>
+        <v>-19.78092205961293</v>
       </c>
       <c r="B41">
-        <v>-14.554321961190155</v>
+        <v>-14.801884008889465</v>
       </c>
       <c r="C41">
         <v>374.58109848544609</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-19.963776195677941</v>
+        <v>-19.78092205961293</v>
       </c>
       <c r="B42">
-        <v>-14.554321961190155</v>
+        <v>-14.801884008889465</v>
       </c>
       <c r="C42">
         <v>374.58109848544609</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-19.30988482897488</v>
+        <v>-19.1556350588411</v>
       </c>
       <c r="B43">
-        <v>-13.610287078322001</v>
+        <v>-13.831846776962724</v>
       </c>
       <c r="C43">
         <v>374.58109848544609</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-18.654006140274966</v>
+        <v>-18.525449611163378</v>
       </c>
       <c r="B44">
-        <v>-12.668427682175635</v>
+        <v>-12.86703944054109</v>
       </c>
       <c r="C44">
         <v>374.58109848544609</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-17.993515124050585</v>
+        <v>-17.888415894133853</v>
       </c>
       <c r="B45">
-        <v>-11.731617320509852</v>
+        <v>-11.909543754891422</v>
       </c>
       <c r="C45">
         <v>374.58109848544609</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-17.325786774774095</v>
+        <v>-17.242584085306614</v>
       </c>
       <c r="B46">
-        <v>-10.802729541083417</v>
+        <v>-10.96144147528055</v>
       </c>
       <c r="C46">
         <v>374.58109848544609</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-16.648567714021635</v>
+        <v>-16.586284880013935</v>
       </c>
       <c r="B47">
-        <v>-9.8842310779475344</v>
+        <v>-10.024514858237158</v>
       </c>
       <c r="C47">
         <v>374.58109848544609</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-15.961091071784381</v>
+        <v>-15.918971044700824</v>
       </c>
       <c r="B48">
-        <v>-8.9769614103230726</v>
+        <v>-9.0993481653373</v>
       </c>
       <c r="C48">
         <v>374.58109848544609</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-15.262961605157276</v>
+        <v>-15.2403758635905</v>
       </c>
       <c r="B49">
-        <v>-8.0813532037233262</v>
+        <v>-8.186226159418867</v>
       </c>
       <c r="C49">
         <v>374.58109848544609</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-14.553784071235262</v>
+        <v>-14.55023262090616</v>
       </c>
       <c r="B50">
-        <v>-7.197839123661578</v>
+        <v>-7.285433603319758</v>
       </c>
       <c r="C50">
         <v>374.58109848544609</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-13.833310476113232</v>
+        <v>-13.848384654374755</v>
       </c>
       <c r="B51">
-        <v>-6.3266906447395836</v>
+        <v>-6.3971377597118755</v>
       </c>
       <c r="C51">
         <v>374.58109848544609</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-13.101881821885888</v>
+        <v>-13.135115515738212</v>
       </c>
       <c r="B52">
-        <v>-5.46753447791294</v>
+        <v>-5.5210358906031454</v>
       </c>
       <c r="C52">
         <v>374.58109848544609</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-12.359986359647881</v>
+        <v>-12.410818810242198</v>
       </c>
       <c r="B53">
-        <v>-4.6198361432257053</v>
+        <v>-4.6567077578355036</v>
       </c>
       <c r="C53">
         <v>374.58109848544609</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-11.608112340493864</v>
+        <v>-11.675888143132379</v>
       </c>
       <c r="B54">
-        <v>-3.7830611607219313</v>
+        <v>-3.8037331232508822</v>
       </c>
       <c r="C54">
         <v>374.58109848544609</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-10.846645946785877</v>
+        <v>-10.930637955134863</v>
       </c>
       <c r="B55">
-        <v>-2.9567867833067121</v>
+        <v>-2.9617762698002537</v>
       </c>
       <c r="C55">
         <v>374.58109848544609</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-10.07556508595553</v>
+        <v>-10.175066028897481</v>
       </c>
       <c r="B56">
-        <v>-2.1410371953292677</v>
+        <v>-2.1308395648707412</v>
       </c>
       <c r="C56">
         <v>374.58109848544609</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-9.2947455967018175</v>
+        <v>-9.4090909825484985</v>
       </c>
       <c r="B57">
-        <v>-1.3359483139998543</v>
+        <v>-1.3110098969585025</v>
       </c>
       <c r="C57">
         <v>374.58109848544609</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-8.5040633177237464</v>
+        <v>-8.6326314342161883</v>
       </c>
       <c r="B58">
-        <v>-0.54165605652873194</v>
+        <v>-0.50237415455970436</v>
       </c>
       <c r="C58">
         <v>374.58109848544609</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-7.7034094736204652</v>
+        <v>-7.8456162491317532</v>
       </c>
       <c r="B59">
-        <v>0.24172050255035329</v>
+        <v>0.29499171429259913</v>
       </c>
       <c r="C59">
         <v>374.58109848544609</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-6.8927368325917815</v>
+        <v>-7.0480152809381753</v>
       </c>
       <c r="B60">
-        <v>1.0141296594096669</v>
+        <v>1.081055523417741</v>
       </c>
       <c r="C60">
         <v>374.58109848544609</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-6.0720135487376554</v>
+        <v>-6.2398086303813685</v>
       </c>
       <c r="B61">
-        <v>1.7755365528979821</v>
+        <v>1.8557960270981591</v>
       </c>
       <c r="C61">
         <v>374.58109848544609</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-5.24120777615806</v>
+        <v>-5.42097639820726</v>
       </c>
       <c r="B62">
-        <v>2.5259063218640678</v>
+        <v>2.6191919796162844</v>
       </c>
       <c r="C62">
         <v>374.58109848544609</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-4.40041035424567</v>
+        <v>-4.5915904807311927</v>
       </c>
       <c r="B63">
-        <v>3.265338406606431</v>
+        <v>3.3713201420810344</v>
       </c>
       <c r="C63">
         <v>374.58109848544609</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-3.5502028635640377</v>
+        <v>-3.7520899565462202</v>
       </c>
       <c r="B64">
-        <v>3.9944694532225173</v>
+        <v>4.1126493029072524</v>
       </c>
       <c r="C64">
         <v>374.58109848544609</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.6912895699694279</v>
+        <v>-2.9030056998148233</v>
       </c>
       <c r="B65">
-        <v>4.7140704092595058</v>
+        <v>4.8437462573362637</v>
       </c>
       <c r="C65">
         <v>374.58109848544609</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.8243747393181058</v>
+        <v>-2.0448685846994796</v>
       </c>
       <c r="B66">
-        <v>5.424912222264572</v>
+        <v>5.5651778006093915</v>
       </c>
       <c r="C66">
         <v>374.58109848544609</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.94922538228715436</v>
+        <v>-1.1774958125359631</v>
       </c>
       <c r="B67">
-        <v>6.1267398428903395</v>
+        <v>6.2767487651703142</v>
       </c>
       <c r="C67">
         <v>374.58109848544609</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.061859488836920641</v>
+        <v>-0.29784989335320977</v>
       </c>
       <c r="B68">
-        <v>6.8151942342111944</v>
+        <v>6.9752161322721316</v>
       </c>
       <c r="C68">
         <v>374.58109848544609</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.84082326255772089</v>
+        <v>0.59643819426427824</v>
       </c>
       <c r="B69">
-        <v>7.4868815283376264</v>
+        <v>7.6580505829918275</v>
       </c>
       <c r="C69">
         <v>374.58109848544609</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.7546474186470413</v>
+        <v>1.5022089062028941</v>
       </c>
       <c r="B70">
-        <v>8.1463725211027658</v>
+        <v>8.3286254488925362</v>
       </c>
       <c r="C70">
         <v>374.58109848544609</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.6750609525747313</v>
+        <v>2.4160178466311026</v>
       </c>
       <c r="B71">
-        <v>8.7986502368976733</v>
+        <v>8.9906181874670725</v>
       </c>
       <c r="C71">
         <v>374.58109848544609</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.6032813178330119</v>
+        <v>3.3388097783747477</v>
       </c>
       <c r="B72">
-        <v>9.4423819506224724</v>
+        <v>9.64302010944081</v>
       </c>
       <c r="C72">
         <v>374.58109848544609</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.5412984399012855</v>
+        <v>4.272118351961268</v>
       </c>
       <c r="B73">
-        <v>10.075389325568423</v>
+        <v>10.284193791329537</v>
       </c>
       <c r="C73">
         <v>374.58109848544609</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.4884226518591648</v>
+        <v>5.2154436100671182</v>
       </c>
       <c r="B74">
-        <v>10.698427328082273</v>
+        <v>10.914673019578096</v>
       </c>
       <c r="C74">
         <v>374.58109848544609</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.4432832024316316</v>
+        <v>6.1677695946285285</v>
       </c>
       <c r="B75">
-        <v>11.312996495672502</v>
+        <v>11.535542496054891</v>
       </c>
       <c r="C75">
         <v>374.58109848544609</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.4044645953249395</v>
+        <v>7.1280499524718159</v>
       </c>
       <c r="B76">
-        <v>11.920646347439025</v>
+        <v>12.14791937439351</v>
       </c>
       <c r="C76">
         <v>374.58109848544609</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8.3706724056143056</v>
+        <v>8.0953323032181626</v>
       </c>
       <c r="B77">
-        <v>12.522793867766213</v>
+        <v>12.752820476855783</v>
       </c>
       <c r="C77">
         <v>374.58109848544609</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9.341141238869529</v>
+        <v>9.0690705527781237</v>
       </c>
       <c r="B78">
-        <v>13.120276920584749</v>
+        <v>13.350828848451416</v>
       </c>
       <c r="C78">
         <v>374.58109848544609</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>10.314475978716674</v>
+        <v>10.04824184678111</v>
       </c>
       <c r="B79">
-        <v>13.714622715451867</v>
+        <v>13.94303655398746</v>
       </c>
       <c r="C79">
         <v>374.58109848544609</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>11.288134296630382</v>
+        <v>11.030955294126295</v>
       </c>
       <c r="B80">
-        <v>14.308614295054221</v>
+        <v>14.531462429854074</v>
       </c>
       <c r="C80">
         <v>374.58109848544609</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>12.255649450782327</v>
+        <v>12.012340092588332</v>
       </c>
       <c r="B81">
-        <v>14.909330688861205</v>
+        <v>15.121306856325674</v>
       </c>
       <c r="C81">
         <v>374.58109848544609</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>13.097614535648118</v>
+        <v>12.901675497178003</v>
       </c>
       <c r="B82">
-        <v>15.647484553337955</v>
+        <v>15.809429108506343</v>
       </c>
       <c r="C82">
         <v>374.58109848544609</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>13.129043759351424</v>
+        <v>12.960144288573401</v>
       </c>
       <c r="B1">
-        <v>18.404777904677427</v>
+        <v>18.524100511895977</v>
       </c>
       <c r="C1">
         <v>442.41419819725974</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>11.581723877164947</v>
+        <v>11.482282949612053</v>
       </c>
       <c r="B2">
-        <v>18.162831560548252</v>
+        <v>18.205563610863688</v>
       </c>
       <c r="C2">
         <v>442.41419819725974</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>10.29948258633792</v>
+        <v>10.230023688555075</v>
       </c>
       <c r="B3">
-        <v>17.669925171531748</v>
+        <v>17.677320392425997</v>
       </c>
       <c r="C3">
         <v>442.41419819725974</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.0682011055759535</v>
+        <v>9.0233531895249275</v>
       </c>
       <c r="B4">
-        <v>17.128773180500417</v>
+        <v>17.106700563415732</v>
       </c>
       <c r="C4">
         <v>442.41419819725974</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.8757608727255919</v>
+        <v>7.852045715977531</v>
       </c>
       <c r="B5">
-        <v>16.550848693925843</v>
+        <v>16.503209362318884</v>
       </c>
       <c r="C5">
         <v>442.41419819725974</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.7171018949426466</v>
+        <v>6.7118113545539391</v>
       </c>
       <c r="B6">
-        <v>15.940942200639254</v>
+        <v>15.870834438277917</v>
       </c>
       <c r="C6">
         <v>442.41419819725974</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.5892656950148147</v>
+        <v>5.6001301827082122</v>
       </c>
       <c r="B7">
-        <v>15.301854604214912</v>
+        <v>15.211918161904675</v>
       </c>
       <c r="C7">
         <v>442.41419819725974</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.4904438144271053</v>
+        <v>4.5154506216146784</v>
       </c>
       <c r="B8">
-        <v>14.635298041524258</v>
+        <v>14.527902788894316</v>
       </c>
       <c r="C8">
         <v>442.41419819725974</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>3.4179329811500314</v>
+        <v>3.4554726870046122</v>
       </c>
       <c r="B9">
-        <v>13.943831803630319</v>
+        <v>13.820926248274644</v>
       </c>
       <c r="C9">
         <v>442.41419819725974</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.368837391238229</v>
+        <v>2.4177362976307659</v>
       </c>
       <c r="B10">
-        <v>13.230197458927526</v>
+        <v>13.093275285733776</v>
       </c>
       <c r="C10">
         <v>442.41419819725974</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.3403859265973912</v>
+        <v>1.3998893897747859</v>
       </c>
       <c r="B11">
-        <v>12.49701853094439</v>
+        <v>12.347136240268503</v>
       </c>
       <c r="C11">
         <v>442.41419819725974</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.331046796303947</v>
+        <v>0.40062311526814759</v>
       </c>
       <c r="B12">
-        <v>11.745745224757696</v>
+        <v>11.583725739544724</v>
       </c>
       <c r="C12">
         <v>442.41419819725974</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.65587916773372079</v>
+        <v>-0.57730652938727933</v>
       </c>
       <c r="B13">
-        <v>10.973252516503225</v>
+        <v>10.800481972596174</v>
       </c>
       <c r="C13">
         <v>442.41419819725974</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.6184517737200932</v>
+        <v>-1.532285704540991</v>
       </c>
       <c r="B14">
-        <v>10.177703552372465</v>
+        <v>9.9959048097559009</v>
       </c>
       <c r="C14">
         <v>442.41419819725974</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.56500601314307</v>
+        <v>-2.4713340426183641</v>
       </c>
       <c r="B15">
-        <v>9.3669893877207748</v>
+        <v>9.1765192851864388</v>
       </c>
       <c r="C15">
         <v>442.41419819725974</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.5031861992327058</v>
+        <v>-3.4008894113895143</v>
       </c>
       <c r="B16">
-        <v>8.5483471863700569</v>
+        <v>8.3483096591151522</v>
       </c>
       <c r="C16">
         <v>442.41419819725974</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-4.4275987489043223</v>
+        <v>-4.3164291479276873</v>
       </c>
       <c r="B17">
-        <v>7.71667063684456</v>
+        <v>7.50707193219928</v>
       </c>
       <c r="C17">
         <v>442.41419819725974</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-5.3312518380242055</v>
+        <v>-5.2120856970994067</v>
       </c>
       <c r="B18">
-        <v>6.8653403117154514</v>
+        <v>6.6473519730290187</v>
       </c>
       <c r="C18">
         <v>442.41419819725974</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-6.2137985745772246</v>
+        <v>-6.087572465641137</v>
       </c>
       <c r="B19">
-        <v>5.9940277950392193</v>
+        <v>5.7688833814965124</v>
       </c>
       <c r="C19">
         <v>442.41419819725974</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-7.0765532995779079</v>
+        <v>-6.9439981007568514</v>
       </c>
       <c r="B20">
-        <v>5.1039774237436744</v>
+        <v>4.8726966903193816</v>
       </c>
       <c r="C20">
         <v>442.41419819725974</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-7.9208303540407723</v>
+        <v>-7.7824712496505111</v>
       </c>
       <c r="B21">
-        <v>4.1964335347566308</v>
+        <v>3.959822432215256</v>
       </c>
       <c r="C21">
         <v>442.41419819725974</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-8.7477067279867065</v>
+        <v>-8.6038997805781214</v>
       </c>
       <c r="B22">
-        <v>3.2724157557386961</v>
+        <v>3.031104507694383</v>
       </c>
       <c r="C22">
         <v>442.41419819725974</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-9.5573100074620445</v>
+        <v>-9.4083884460038849</v>
       </c>
       <c r="B23">
-        <v>2.3320448772816329</v>
+        <v>2.086640288437509</v>
       </c>
       <c r="C23">
         <v>442.41419819725974</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-10.349530427519481</v>
+        <v>-10.195841219444032</v>
       </c>
       <c r="B24">
-        <v>1.3752169807100039</v>
+        <v>1.1263405139180072</v>
       </c>
       <c r="C24">
         <v>442.41419819725974</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-11.12425822321171</v>
+        <v>-10.966162074414811</v>
       </c>
       <c r="B25">
-        <v>0.40182814734836519</v>
+        <v>0.15011592360924653</v>
       </c>
       <c r="C25">
         <v>442.41419819725974</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-11.881338342810309</v>
+        <v>-11.719215650951471</v>
       </c>
       <c r="B26">
-        <v>-0.58826841620717407</v>
+        <v>-0.84215930508754322</v>
       </c>
       <c r="C26">
         <v>442.41419819725974</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-12.620434587462377</v>
+        <v>-12.454709255165337</v>
       </c>
       <c r="B27">
-        <v>-1.595391002274323</v>
+        <v>-1.8507572430597179</v>
       </c>
       <c r="C27">
         <v>442.41419819725974</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-13.341165471533881</v>
+        <v>-13.172310859686732</v>
       </c>
       <c r="B28">
-        <v>-2.6199007778992334</v>
+        <v>-2.8759865232667692</v>
       </c>
       <c r="C28">
         <v>442.41419819725974</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-14.043149509390787</v>
+        <v>-13.871688437145982</v>
       </c>
       <c r="B29">
-        <v>-3.6621589101280496</v>
+        <v>-3.9181557786681842</v>
       </c>
       <c r="C29">
         <v>442.41419819725974</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-14.726168362151837</v>
+        <v>-14.552645700129943</v>
       </c>
       <c r="B30">
-        <v>-4.7223721087337704</v>
+        <v>-4.9774474664068675</v>
       </c>
       <c r="C30">
         <v>442.41419819725974</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-15.390656277946793</v>
+        <v>-15.215529321051511</v>
       </c>
       <c r="B31">
-        <v>-5.8001292543967136</v>
+        <v>-6.0535393403593138</v>
       </c>
       <c r="C31">
         <v>442.41419819725974</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-16.037210651658189</v>
+        <v>-15.860821712280121</v>
       </c>
       <c r="B32">
-        <v>-6.8948647705240527</v>
+        <v>-7.1459829785854421</v>
       </c>
       <c r="C32">
         <v>442.41419819725974</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-16.666428878168549</v>
+        <v>-16.489005286185179</v>
       </c>
       <c r="B33">
-        <v>-8.0060130805229388</v>
+        <v>-8.2543299591451529</v>
       </c>
       <c r="C33">
         <v>442.41419819725974</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-17.27862182289342</v>
+        <v>-17.100319949471967</v>
       </c>
       <c r="B34">
-        <v>-9.1332798762101479</v>
+        <v>-9.37835727898747</v>
       </c>
       <c r="C34">
         <v>442.41419819725974</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-17.872954233380394</v>
+        <v>-17.694035586189059</v>
       </c>
       <c r="B35">
-        <v>-10.277455923040829</v>
+        <v>-10.518743610617856</v>
       </c>
       <c r="C35">
         <v>442.41419819725974</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-18.448304327710058</v>
+        <v>-18.26917957472088</v>
       </c>
       <c r="B36">
-        <v>-11.439603254879739</v>
+        <v>-11.676393045430872</v>
       </c>
       <c r="C36">
         <v>442.41419819725974</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-19.003550323963022</v>
+        <v>-18.824779293451861</v>
       </c>
       <c r="B37">
-        <v>-12.620783905591644</v>
+        <v>-12.8522096748211</v>
       </c>
       <c r="C37">
         <v>442.41419819725974</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-19.536881321491226</v>
+        <v>-19.359281122838937</v>
       </c>
       <c r="B38">
-        <v>-13.822712324108821</v>
+        <v>-14.047637651413613</v>
       </c>
       <c r="C38">
         <v>442.41419819725974</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-20.043729944731908</v>
+        <v>-19.868807451629035</v>
       </c>
       <c r="B39">
-        <v>-15.049712619633615</v>
+        <v>-15.266281372755458</v>
       </c>
       <c r="C39">
         <v>442.41419819725974</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-20.518839699393666</v>
+        <v>-20.348899670641604</v>
       </c>
       <c r="B40">
-        <v>-16.306761316435907</v>
+        <v>-16.512285297624196</v>
       </c>
       <c r="C40">
         <v>442.41419819725974</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-20.956954091185075</v>
+        <v>-20.795099170696076</v>
       </c>
       <c r="B41">
-        <v>-17.598834938785551</v>
+        <v>-17.789793884797366</v>
       </c>
       <c r="C41">
         <v>442.41419819725974</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-20.956954091185075</v>
+        <v>-20.795099170696076</v>
       </c>
       <c r="B42">
-        <v>-17.598834938785551</v>
+        <v>-17.789793884797366</v>
       </c>
       <c r="C42">
         <v>442.41419819725974</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-20.281816529902944</v>
+        <v>-20.149678128073127</v>
       </c>
       <c r="B43">
-        <v>-16.531160219982468</v>
+        <v>-16.697469833280678</v>
       </c>
       <c r="C43">
         <v>442.41419819725974</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-19.610390460547986</v>
+        <v>-19.5045790908302</v>
       </c>
       <c r="B44">
-        <v>-15.459971689762673</v>
+        <v>-15.60484646465193</v>
       </c>
       <c r="C44">
         <v>442.41419819725974</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-18.937900600756738</v>
+        <v>-18.8558288088314</v>
       </c>
       <c r="B45">
-        <v>-14.389790290651714</v>
+        <v>-14.515617076693992</v>
       </c>
       <c r="C45">
         <v>442.41419819725974</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-18.259571668165705</v>
+        <v>-18.1994540319408</v>
       </c>
       <c r="B46">
-        <v>-13.325136965175128</v>
+        <v>-13.433474967189721</v>
       </c>
       <c r="C46">
         <v>442.41419819725974</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-17.571296282854984</v>
+        <v>-17.53204110882152</v>
       </c>
       <c r="B47">
-        <v>-12.269900327059844</v>
+        <v>-12.361593264052729</v>
       </c>
       <c r="C47">
         <v>442.41419819725974</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-16.871638674678891</v>
+        <v>-16.852414783332733</v>
       </c>
       <c r="B48">
-        <v>-11.225439674838258</v>
+        <v>-11.301064415719608</v>
       </c>
       <c r="C48">
         <v>442.41419819725974</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.159830975935304</v>
+        <v>-16.159959398132628</v>
       </c>
       <c r="B49">
-        <v>-10.192481978244146</v>
+        <v>-10.252460700757693</v>
       </c>
       <c r="C49">
         <v>442.41419819725974</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-15.435105318922112</v>
+        <v>-15.454059295879421</v>
       </c>
       <c r="B50">
-        <v>-9.1717542070112881</v>
+        <v>-9.2163543977343334</v>
       </c>
       <c r="C50">
         <v>442.41419819725974</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-14.696960456978111</v>
+        <v>-14.73432124489724</v>
       </c>
       <c r="B51">
-        <v>-8.1637309105325748</v>
+        <v>-8.193111031503733</v>
       </c>
       <c r="C51">
         <v>442.41419819725974</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-13.945961627605701</v>
+        <v>-14.001241716173928</v>
       </c>
       <c r="B52">
-        <v>-7.16787695683733</v>
+        <v>-7.1822691120675328</v>
       </c>
       <c r="C52">
         <v>442.41419819725974</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-13.182940689348209</v>
+        <v>-13.255539606363278</v>
       </c>
       <c r="B53">
-        <v>-6.1834047936139962</v>
+        <v>-6.1831603957142391</v>
       </c>
       <c r="C53">
         <v>442.41419819725974</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-12.408729500748942</v>
+        <v>-12.497933812119072</v>
       </c>
       <c r="B54">
-        <v>-5.209526868551003</v>
+        <v>-5.1951166387323475</v>
       </c>
       <c r="C54">
         <v>442.41419819725974</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-11.623980267701279</v>
+        <v>-11.728990841992465</v>
       </c>
       <c r="B55">
-        <v>-4.245625713374384</v>
+        <v>-4.217611248356663</v>
       </c>
       <c r="C55">
         <v>442.41419819725974</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-10.828626585498776</v>
+        <v>-10.948667652124048</v>
       </c>
       <c r="B56">
-        <v>-3.2917641959604844</v>
+        <v>-3.2506842356071277</v>
       </c>
       <c r="C56">
         <v>442.41419819725974</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-10.022422396785064</v>
+        <v>-10.156768810551803</v>
       </c>
       <c r="B57">
-        <v>-2.3481752682232528</v>
+        <v>-2.2945172624499928</v>
       </c>
       <c r="C57">
         <v>442.41419819725974</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-9.20512164420376</v>
+        <v>-9.3530988853136954</v>
       </c>
       <c r="B58">
-        <v>-1.4150918820766316</v>
+        <v>-1.3492919908515031</v>
       </c>
       <c r="C58">
         <v>442.41419819725974</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-8.3765084562054071</v>
+        <v>-8.5374865468132679</v>
       </c>
       <c r="B59">
-        <v>-0.49271841137616973</v>
+        <v>-0.41516767864769633</v>
       </c>
       <c r="C59">
         <v>442.41419819725974</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-7.5364877044682537</v>
+        <v>-7.7098568749164009</v>
       </c>
       <c r="B60">
-        <v>0.41885508225612733</v>
+        <v>0.50778603284617774</v>
       </c>
       <c r="C60">
         <v>442.41419819725974</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-6.6849944464774769</v>
+        <v>-6.8701590518545421</v>
       </c>
       <c r="B61">
-        <v>1.3195671152566426</v>
+        <v>1.4195219064450744</v>
       </c>
       <c r="C61">
         <v>442.41419819725974</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-5.8219637397182566</v>
+        <v>-6.0183422598591472</v>
       </c>
       <c r="B62">
-        <v>2.2093562040617556</v>
+        <v>2.3199927049639428</v>
       </c>
       <c r="C62">
         <v>442.41419819725974</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-4.9475527417319531</v>
+        <v>-5.15454107773857</v>
       </c>
       <c r="B63">
-        <v>3.0883711357290453</v>
+        <v>3.2093235248848897</v>
       </c>
       <c r="C63">
         <v>442.41419819725974</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.0628070102846925</v>
+        <v>-4.2796316706087776</v>
       </c>
       <c r="B64">
-        <v>3.9576017798008749</v>
+        <v>4.0883287973586144</v>
       </c>
       <c r="C64">
         <v>442.41419819725974</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.1689942031987868</v>
+        <v>-3.3946756001626404</v>
       </c>
       <c r="B65">
-        <v>4.8182482764407943</v>
+        <v>4.9579952872029676</v>
       </c>
       <c r="C65">
         <v>442.41419819725974</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.2673819782965432</v>
+        <v>-2.50073442809302</v>
       </c>
       <c r="B66">
-        <v>5.6715107658123705</v>
+        <v>5.8193097592358063</v>
       </c>
       <c r="C66">
         <v>442.41419819725974</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.3575642572586262</v>
+        <v>-1.5974618647606378</v>
       </c>
       <c r="B67">
-        <v>6.5170047980332866</v>
+        <v>6.6719503231372972</v>
       </c>
       <c r="C67">
         <v>442.41419819725974</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.43244001719907083</v>
+        <v>-0.67888021519758091</v>
       </c>
       <c r="B68">
-        <v>7.348007563037795</v>
+        <v>7.5103604680368967</v>
       </c>
       <c r="C68">
         <v>442.41419819725974</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.5135119236507123</v>
+        <v>0.25966188186083827</v>
       </c>
       <c r="B69">
-        <v>8.1592919467939</v>
+        <v>8.3302165642464381</v>
       </c>
       <c r="C69">
         <v>442.41419819725974</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.4727984380231862</v>
+        <v>1.2118790475378025</v>
       </c>
       <c r="B70">
-        <v>8.9579519795881026</v>
+        <v>9.1373611273579662</v>
       </c>
       <c r="C70">
         <v>442.41419819725974</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.4372504635044692</v>
+        <v>2.1709190084698533</v>
       </c>
       <c r="B71">
-        <v>9.75172162537261</v>
+        <v>9.9381636244714979</v>
       </c>
       <c r="C71">
         <v>442.41419819725974</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.4090095061313996</v>
+        <v>3.1385986534884638</v>
       </c>
       <c r="B72">
-        <v>10.538573438443963</v>
+        <v>10.73093518343868</v>
       </c>
       <c r="C72">
         <v>442.41419819725974</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.3915953399263463</v>
+        <v>4.1178948080673354</v>
       </c>
       <c r="B73">
-        <v>11.315175114061452</v>
+        <v>11.512908723772274</v>
       </c>
       <c r="C73">
         <v>442.41419819725974</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.38373024240311</v>
+        <v>5.1077548820541594</v>
       </c>
       <c r="B74">
-        <v>12.082736320991028</v>
+        <v>12.285062670877881</v>
       </c>
       <c r="C74">
         <v>442.41419819725974</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.3829155145998122</v>
+        <v>6.1061015785894055</v>
       </c>
       <c r="B75">
-        <v>12.843622673145214</v>
+        <v>13.049327956769149</v>
       </c>
       <c r="C75">
         <v>442.41419819725974</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.3865660481604865</v>
+        <v>7.1107881896106564</v>
       </c>
       <c r="B76">
-        <v>13.600281591516128</v>
+        <v>13.807700033999064</v>
       </c>
       <c r="C76">
         <v>442.41419819725974</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8.3923098373116716</v>
+        <v>8.11984885198007</v>
       </c>
       <c r="B77">
-        <v>14.354958744727279</v>
+        <v>14.562006252399636</v>
       </c>
       <c r="C77">
         <v>442.41419819725974</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9.3987136960040765</v>
+        <v>9.1321104934609725</v>
       </c>
       <c r="B78">
-        <v>15.109010984848148</v>
+        <v>15.313337030379635</v>
       </c>
       <c r="C78">
         <v>442.41419819725974</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>10.403215069811562</v>
+        <v>10.145452526382753</v>
       </c>
       <c r="B79">
-        <v>15.864864380202524</v>
+        <v>16.06366354052431</v>
       </c>
       <c r="C79">
         <v>442.41419819725974</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>11.401193139347885</v>
+        <v>11.156027995670755</v>
       </c>
       <c r="B80">
-        <v>16.626893637305329</v>
+        <v>16.816561684214626</v>
       </c>
       <c r="C80">
         <v>442.41419819725974</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>12.381004082289826</v>
+        <v>12.15408999595088</v>
       </c>
       <c r="B81">
-        <v>17.406122408266341</v>
+        <v>17.5810916068672</v>
       </c>
       <c r="C81">
         <v>442.41419819725974</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>13.129043759351424</v>
+        <v>12.960144288573401</v>
       </c>
       <c r="B82">
-        <v>18.404777904677427</v>
+        <v>18.524100511895977</v>
       </c>
       <c r="C82">
         <v>442.41419819725974</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>13.122097664590044</v>
+        <v>12.993376814575044</v>
       </c>
       <c r="B1">
-        <v>20.699399983615979</v>
+        <v>20.780405572258083</v>
       </c>
       <c r="C1">
         <v>501.14832753435888</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>11.305860553161706</v>
+        <v>11.25464323645299</v>
       </c>
       <c r="B2">
-        <v>20.480921938910168</v>
+        <v>20.486694695511492</v>
       </c>
       <c r="C2">
         <v>501.14832753435888</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9.8853362187583009</v>
+        <v>9.86639517117221</v>
       </c>
       <c r="B3">
-        <v>19.925739262999848</v>
+        <v>19.898497575296947</v>
       </c>
       <c r="C3">
         <v>501.14832753435888</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>8.5360924045754238</v>
+        <v>8.5432206176066412</v>
       </c>
       <c r="B4">
-        <v>19.309905320144448</v>
+        <v>19.255624146612668</v>
       </c>
       <c r="C4">
         <v>501.14832753435888</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.2398419626237631</v>
+        <v>7.26899883343054</v>
       </c>
       <c r="B5">
-        <v>18.648980303941492</v>
+        <v>18.571619439639615</v>
       </c>
       <c r="C5">
         <v>501.14832753435888</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>5.9889898791680363</v>
+        <v>6.0370166371410354</v>
       </c>
       <c r="B6">
-        <v>17.949426670109396</v>
+        <v>17.852124028752673</v>
       </c>
       <c r="C6">
         <v>501.14832753435888</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>4.7791190644576087</v>
+        <v>4.8433594027797371</v>
       </c>
       <c r="B7">
-        <v>17.215002838041794</v>
+        <v>17.100427075560038</v>
       </c>
       <c r="C7">
         <v>501.14832753435888</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.6075519771635891</v>
+        <v>3.6856441650548439</v>
       </c>
       <c r="B8">
-        <v>16.447987077782084</v>
+        <v>16.318530804037842</v>
       </c>
       <c r="C8">
         <v>501.14832753435888</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.4702475856207959</v>
+        <v>2.5602918908507015</v>
       </c>
       <c r="B9">
-        <v>15.651817827903654</v>
+        <v>15.509442402725581</v>
       </c>
       <c r="C9">
         <v>501.14832753435888</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>1.3628696270873197</v>
+        <v>1.4634653867269869</v>
       </c>
       <c r="B10">
-        <v>14.830184733603966</v>
+        <v>14.67638597259263</v>
       </c>
       <c r="C10">
         <v>501.14832753435888</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.28126440485060683</v>
+        <v>0.3914908857685605</v>
       </c>
       <c r="B11">
-        <v>13.986622098046661</v>
+        <v>13.822448299764451</v>
       </c>
       <c r="C11">
         <v>501.14832753435888</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.77684653294076211</v>
+        <v>-0.657654534533497</v>
       </c>
       <c r="B12">
-        <v>13.123068613472405</v>
+        <v>12.949329091728661</v>
       </c>
       <c r="C12">
         <v>501.14832753435888</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.8064232247230663</v>
+        <v>-1.6795538455883929</v>
       </c>
       <c r="B13">
-        <v>12.235235870463754</v>
+        <v>12.053317056265371</v>
       </c>
       <c r="C13">
         <v>501.14832753435888</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.8044908713063705</v>
+        <v>-2.6716052514485984</v>
       </c>
       <c r="B14">
-        <v>11.320592667800257</v>
+        <v>11.132226102689561</v>
       </c>
       <c r="C14">
         <v>501.14832753435888</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-3.7836537364110439</v>
+        <v>-3.6449078378393667</v>
       </c>
       <c r="B15">
-        <v>10.389863738707552</v>
+        <v>10.195381946163206</v>
       </c>
       <c r="C15">
         <v>501.14832753435888</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-4.7554717891518452</v>
+        <v>-4.6096410285356857</v>
       </c>
       <c r="B16">
-        <v>9.4528852455829853</v>
+        <v>9.2513375800578856</v>
       </c>
       <c r="C16">
         <v>501.14832753435888</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-5.7117487573108345</v>
+        <v>-5.558604717838759</v>
       </c>
       <c r="B17">
-        <v>8.5026831330646253</v>
+        <v>8.2940433047365936</v>
       </c>
       <c r="C17">
         <v>501.14832753435888</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-6.6418692049854169</v>
+        <v>-6.4824695209920113</v>
       </c>
       <c r="B18">
-        <v>7.53022492447197</v>
+        <v>7.3156603497789554</v>
       </c>
       <c r="C18">
         <v>501.14832753435888</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.5452972828671037</v>
+        <v>-7.380768466481582</v>
       </c>
       <c r="B19">
-        <v>6.5350546756094463</v>
+        <v>6.3157963546397129</v>
       </c>
       <c r="C19">
         <v>501.14832753435888</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-8.4240170382959363</v>
+        <v>-8.2552501861042877</v>
       </c>
       <c r="B20">
-        <v>5.5188605754027256</v>
+        <v>5.2959205612423794</v>
       </c>
       <c r="C20">
         <v>501.14832753435888</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-9.2800125186119526</v>
+        <v>-9.107663311656939</v>
       </c>
       <c r="B21">
-        <v>4.4833308127774831</v>
+        <v>4.2575022115104826</v>
       </c>
       <c r="C21">
         <v>501.14832753435888</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-10.114910645386196</v>
+        <v>-9.9394412184596348</v>
       </c>
       <c r="B22">
-        <v>3.4298497049945698</v>
+        <v>3.2017456613960555</v>
       </c>
       <c r="C22">
         <v>501.14832753435888</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-10.928909837113732</v>
+        <v>-10.750756255925591</v>
       </c>
       <c r="B23">
-        <v>2.3585860826555867</v>
+        <v>2.1287957229652328</v>
       </c>
       <c r="C23">
         <v>501.14832753435888</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-11.721851386520626</v>
+        <v>-11.541465516991318</v>
       </c>
       <c r="B24">
-        <v>1.269404904697317</v>
+        <v>1.038532322312673</v>
       </c>
       <c r="C24">
         <v>501.14832753435888</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-12.493576586332953</v>
+        <v>-12.311426094593323</v>
       </c>
       <c r="B25">
-        <v>0.16217113005654021</v>
+        <v>-0.069164614466973862</v>
       </c>
       <c r="C25">
         <v>501.14832753435888</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-13.243860664698406</v>
+        <v>-13.060435855837268</v>
       </c>
       <c r="B26">
-        <v>-0.963306495449138</v>
+        <v>-1.1944649242273024</v>
       </c>
       <c r="C26">
         <v>501.14832753435888</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-13.972214591451193</v>
+        <v>-13.78805576450547</v>
       </c>
       <c r="B27">
-        <v>-2.1074440784788475</v>
+        <v>-2.3377374956149364</v>
       </c>
       <c r="C27">
         <v>501.14832753435888</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-14.67808327184715</v>
+        <v>-14.493787558549409</v>
       </c>
       <c r="B28">
-        <v>-3.2707139388108959</v>
+        <v>-3.4994009802247534</v>
       </c>
       <c r="C28">
         <v>501.14832753435888</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-15.360911611142113</v>
+        <v>-15.177132975920573</v>
       </c>
       <c r="B29">
-        <v>-4.4535883962235978</v>
+        <v>-4.6798740296516259</v>
       </c>
       <c r="C29">
         <v>501.14832753435888</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-16.020394573537342</v>
+        <v>-15.837812488189382</v>
       </c>
       <c r="B30">
-        <v>-5.6563269999963124</v>
+        <v>-5.8793915103141305</v>
       </c>
       <c r="C30">
         <v>501.14832753435888</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-16.657227359015849</v>
+        <v>-16.476421501402097</v>
       </c>
       <c r="B31">
-        <v>-6.8783382174126908</v>
+        <v>-7.0974531479256662</v>
       </c>
       <c r="C31">
         <v>501.14832753435888</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-17.272355226506072</v>
+        <v>-17.09377415522394</v>
       </c>
       <c r="B32">
-        <v>-8.11881774525744</v>
+        <v>-8.3333748830233443</v>
       </c>
       <c r="C32">
         <v>501.14832753435888</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-17.866723434936457</v>
+        <v>-17.69068458932011</v>
       </c>
       <c r="B33">
-        <v>-9.3769612803152711</v>
+        <v>-9.5864726561442772</v>
       </c>
       <c r="C33">
         <v>501.14832753435888</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-18.440846308770379</v>
+        <v>-18.267586411767823</v>
       </c>
       <c r="B34">
-        <v>-10.652331193480375</v>
+        <v>-10.856382139494242</v>
       </c>
       <c r="C34">
         <v>501.14832753435888</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-18.993514434611022</v>
+        <v>-18.823391104292281</v>
       </c>
       <c r="B35">
-        <v>-11.945956552084907</v>
+        <v>-12.144017931953785</v>
       </c>
       <c r="C35">
         <v>501.14832753435888</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-19.523087464596493</v>
+        <v>-19.356629617030709</v>
       </c>
       <c r="B36">
-        <v>-13.259233097570517</v>
+        <v>-13.450614364072127</v>
       </c>
       <c r="C36">
         <v>501.14832753435888</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-20.027925050864912</v>
+        <v>-19.865832900120303</v>
       </c>
       <c r="B37">
-        <v>-14.593556571378853</v>
+        <v>-14.777405766398491</v>
       </c>
       <c r="C37">
         <v>501.14832753435888</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-20.505345917678287</v>
+        <v>-20.348614712803563</v>
       </c>
       <c r="B38">
-        <v>-15.951208421092447</v>
+        <v>-16.126397115033015</v>
       </c>
       <c r="C38">
         <v>501.14832753435888</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-20.948505077794142</v>
+        <v>-20.7989200507441</v>
       </c>
       <c r="B39">
-        <v>-17.338012918857377</v>
+        <v>-17.502675968279448</v>
       </c>
       <c r="C39">
         <v>501.14832753435888</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-21.34951661609389</v>
+        <v>-21.20977671871082</v>
       </c>
       <c r="B40">
-        <v>-18.760680042960605</v>
+        <v>-18.912100529992465</v>
       </c>
       <c r="C40">
         <v>501.14832753435888</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-21.700494617458954</v>
+        <v>-21.574212521472624</v>
       </c>
       <c r="B41">
-        <v>-20.225919771689107</v>
+        <v>-20.360529004026731</v>
       </c>
       <c r="C41">
         <v>501.14832753435888</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-21.700494617458954</v>
+        <v>-21.574212521472624</v>
       </c>
       <c r="B42">
-        <v>-20.225919771689107</v>
+        <v>-20.360529004026731</v>
       </c>
       <c r="C42">
         <v>501.14832753435888</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-20.990284185985704</v>
+        <v>-20.893792305052351</v>
       </c>
       <c r="B43">
-        <v>-19.066344226476861</v>
+        <v>-19.17759813135795</v>
       </c>
       <c r="C43">
         <v>501.14832753435888</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-20.291735546361007</v>
+        <v>-20.221219047423912</v>
       </c>
       <c r="B44">
-        <v>-17.896845879799695</v>
+        <v>-17.988074057736227</v>
       </c>
       <c r="C44">
         <v>501.14832753435888</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-19.597530448162232</v>
+        <v>-19.550091208790484</v>
       </c>
       <c r="B45">
-        <v>-16.723651694628426</v>
+        <v>-16.797335508781064</v>
       </c>
       <c r="C45">
         <v>501.14832753435888</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-18.900350640966749</v>
+        <v>-18.874007249355227</v>
       </c>
       <c r="B46">
-        <v>-15.552988633933868</v>
+        <v>-15.610761210111928</v>
       </c>
       <c r="C46">
         <v>501.14832753435888</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-18.193893648419586</v>
+        <v>-18.187457533884871</v>
       </c>
       <c r="B47">
-        <v>-14.39021935745305</v>
+        <v>-14.432980487972813</v>
       </c>
       <c r="C47">
         <v>501.14832753435888</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-17.475920090436333</v>
+        <v>-17.488500045400304</v>
       </c>
       <c r="B48">
-        <v>-13.237249311987858</v>
+        <v>-13.265625071105621</v>
       </c>
       <c r="C48">
         <v>501.14832753435888</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.745206361000236</v>
+        <v>-16.776084671485986</v>
       </c>
       <c r="B49">
-        <v>-12.095119641106381</v>
+        <v>-12.109577288876743</v>
       </c>
       <c r="C49">
         <v>501.14832753435888</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-16.00052885409454</v>
+        <v>-16.049161299726347</v>
       </c>
       <c r="B50">
-        <v>-10.964871488376705</v>
+        <v>-10.965719470652578</v>
       </c>
       <c r="C50">
         <v>501.14832753435888</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-15.241071384414246</v>
+        <v>-15.307036711658459</v>
       </c>
       <c r="B51">
-        <v>-9.8471993306721348</v>
+        <v>-9.8346340750328967</v>
       </c>
       <c r="C51">
         <v>501.14832753435888</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-14.467647449501378</v>
+        <v>-14.550445264629882</v>
       </c>
       <c r="B52">
-        <v>-8.74141097808683</v>
+        <v>-8.7157040775510151</v>
       </c>
       <c r="C52">
         <v>501.14832753435888</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-13.681477967609705</v>
+        <v>-13.780478209940796</v>
       </c>
       <c r="B53">
-        <v>-7.64646757402015</v>
+        <v>-7.6080125829736138</v>
       </c>
       <c r="C53">
         <v>501.14832753435888</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-12.883783856993007</v>
+        <v>-12.998226798891375</v>
       </c>
       <c r="B54">
-        <v>-6.5613302618714586</v>
+        <v>-6.5106426960673831</v>
       </c>
       <c r="C54">
         <v>501.14832753435888</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-12.075516547910247</v>
+        <v>-12.204544017751628</v>
       </c>
       <c r="B55">
-        <v>-5.4851894873552594</v>
+        <v>-5.4228777175303993</v>
       </c>
       <c r="C55">
         <v>501.14832753435888</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-11.256549518641187</v>
+        <v>-11.399329792670917</v>
       </c>
       <c r="B56">
-        <v>-4.4181529054466635</v>
+        <v>-4.3448017317863261</v>
       </c>
       <c r="C56">
         <v>501.14832753435888</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-10.426486759470759</v>
+        <v>-10.582245784768421</v>
       </c>
       <c r="B57">
-        <v>-3.3605574734359105</v>
+        <v>-3.2766990191902123</v>
       </c>
       <c r="C57">
         <v>501.14832753435888</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-9.58493226068391</v>
+        <v>-9.7529536551633242</v>
       </c>
       <c r="B58">
-        <v>-2.3127401486132455</v>
+        <v>-2.2188538600971048</v>
       </c>
       <c r="C58">
         <v>501.14832753435888</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-8.7315383342780848</v>
+        <v>-8.9111564544615955</v>
       </c>
       <c r="B59">
-        <v>-1.2749967722238058</v>
+        <v>-1.1715157584332547</v>
       </c>
       <c r="C59">
         <v>501.14832753435888</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-7.8661505791007693</v>
+        <v>-8.0567227912163268</v>
       </c>
       <c r="B60">
-        <v>-0.24745872133231495</v>
+        <v>-0.13479511240973696</v>
       </c>
       <c r="C60">
         <v>501.14832753435888</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-6.9886629157119469</v>
+        <v>-7.189562663467389</v>
       </c>
       <c r="B61">
-        <v>0.76978374304161912</v>
+        <v>0.89123245619117641</v>
       </c>
       <c r="C61">
         <v>501.14832753435888</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-6.0989692646715987</v>
+        <v>-6.3095860692546548</v>
       </c>
       <c r="B62">
-        <v>1.7766403598783791</v>
+        <v>1.906491325587208</v>
       </c>
       <c r="C62">
         <v>501.14832753435888</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.1973027650036512</v>
+        <v>-5.4170002614451187</v>
       </c>
       <c r="B63">
-        <v>2.7733095028308394</v>
+        <v>2.91115563455446</v>
       </c>
       <c r="C63">
         <v>501.14832753435888</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-4.28525342958775</v>
+        <v>-4.5132015122142439</v>
       </c>
       <c r="B64">
-        <v>3.761144084241836</v>
+        <v>3.9063985641025565</v>
       </c>
       <c r="C64">
         <v>501.14832753435888</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-3.3647504897674816</v>
+        <v>-3.5998833485646169</v>
       </c>
       <c r="B65">
-        <v>4.7417856511266843</v>
+        <v>4.8936430557994877</v>
       </c>
       <c r="C65">
         <v>501.14832753435888</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-2.4377231768864274</v>
+        <v>-2.6787392974988218</v>
       </c>
       <c r="B66">
-        <v>5.7168757505007068</v>
+        <v>5.8743120512132556</v>
       </c>
       <c r="C66">
         <v>501.14832753435888</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.5035661380506413</v>
+        <v>-1.7492325177382821</v>
       </c>
       <c r="B67">
-        <v>6.685899298862088</v>
+        <v>6.8479544835645711</v>
       </c>
       <c r="C67">
         <v>501.14832753435888</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.55153568341606907</v>
+        <v>-0.80190469487978044</v>
       </c>
       <c r="B68">
-        <v>7.63971469064045</v>
+        <v>7.8066232526849673</v>
       </c>
       <c r="C68">
         <v>501.14832753435888</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.42671433768030032</v>
+        <v>0.17059494485430898</v>
       </c>
       <c r="B69">
-        <v>8.5712203416966819</v>
+        <v>8.7441420640428849</v>
       </c>
       <c r="C69">
         <v>501.14832753435888</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.419801582227145</v>
+        <v>1.1582655396145807</v>
       </c>
       <c r="B70">
-        <v>9.4901012756852676</v>
+        <v>9.6689138790434743</v>
       </c>
       <c r="C70">
         <v>501.14832753435888</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.4153167618836164</v>
+        <v>2.1502040062820114</v>
       </c>
       <c r="B71">
-        <v>10.406916324913144</v>
+        <v>10.59009972680864</v>
       </c>
       <c r="C71">
         <v>501.14832753435888</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.4164713006650191</v>
+        <v>3.1492500122860827</v>
       </c>
       <c r="B72">
-        <v>11.318932948503452</v>
+        <v>11.505313651390503</v>
       </c>
       <c r="C72">
         <v>501.14832753435888</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.4285625506490751</v>
+        <v>4.1600793327920895</v>
       </c>
       <c r="B73">
-        <v>12.221643728244677</v>
+        <v>12.410626955558282</v>
       </c>
       <c r="C73">
         <v>501.14832753435888</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.4496108638070071</v>
+        <v>5.1809694233600441</v>
       </c>
       <c r="B74">
-        <v>13.116733109770486</v>
+        <v>13.307486962019345</v>
       </c>
       <c r="C74">
         <v>501.14832753435888</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.4757829995768912</v>
+        <v>6.2085686615468934</v>
       </c>
       <c r="B75">
-        <v>14.007462726074952</v>
+        <v>14.198709783470557</v>
       </c>
       <c r="C75">
         <v>501.14832753435888</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>7.5031083473707154</v>
+        <v>7.2394074325025652</v>
       </c>
       <c r="B76">
-        <v>14.897211095748615</v>
+        <v>15.08721067262862</v>
       </c>
       <c r="C76">
         <v>501.14832753435888</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8.5279358453653131</v>
+        <v>8.27029872750738</v>
       </c>
       <c r="B77">
-        <v>15.789084839290105</v>
+        <v>15.975667429834417</v>
       </c>
       <c r="C77">
         <v>501.14832753435888</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9.5480299968229687</v>
+        <v>9.2993039547701954</v>
       </c>
       <c r="B78">
-        <v>16.684986099233932</v>
+        <v>16.865708905905663</v>
       </c>
       <c r="C78">
         <v>501.14832753435888</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>10.559440213277707</v>
+        <v>10.322977447376722</v>
       </c>
       <c r="B79">
-        <v>17.588276357719948</v>
+        <v>17.760230231935246</v>
       </c>
       <c r="C79">
         <v>501.14832753435888</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>11.555089264774749</v>
+        <v>11.335126535545578</v>
       </c>
       <c r="B80">
-        <v>18.504977497892252</v>
+        <v>18.664434636000045</v>
       </c>
       <c r="C80">
         <v>501.14832753435888</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>12.517250017918739</v>
+        <v>12.32019344197877</v>
       </c>
       <c r="B81">
-        <v>19.450173207361516</v>
+        <v>19.591394131707855</v>
       </c>
       <c r="C81">
         <v>501.14832753435888</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>13.122097664590044</v>
+        <v>12.993376814575044</v>
       </c>
       <c r="B82">
-        <v>20.699399983615979</v>
+        <v>20.780405572258083</v>
       </c>
       <c r="C82">
         <v>501.14832753435888</v>
